--- a/audit-autogen-project/data/t.xlsx
+++ b/audit-autogen-project/data/t.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\审计自动化\audit_autogen_project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DCA00B8-7107-429C-BFC9-0206CB9CFE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D67DE95-D889-4A69-A1B3-389FEB1D7001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{EEA8E8F9-6914-45C3-A810-71A68AF4BF67}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{EEA8E8F9-6914-45C3-A810-71A68AF4BF67}"/>
   </bookViews>
   <sheets>
     <sheet name="资产负债表" sheetId="1" r:id="rId1"/>
     <sheet name="业务活动表" sheetId="2" r:id="rId2"/>
+    <sheet name="资产负债变动" sheetId="3" r:id="rId3"/>
+    <sheet name="收入汇总" sheetId="4" r:id="rId4"/>
+    <sheet name="支出汇总" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="93">
   <si>
     <t>会民非01表</t>
   </si>
@@ -275,6 +278,45 @@
   </si>
   <si>
     <t>资产负债表(负债及净资产)</t>
+  </si>
+  <si>
+    <t>项  目</t>
+  </si>
+  <si>
+    <t>本届期初余额</t>
+  </si>
+  <si>
+    <t>本届期末余额</t>
+  </si>
+  <si>
+    <t>本届变动额</t>
+  </si>
+  <si>
+    <t>限定性净资产</t>
+  </si>
+  <si>
+    <t>非限定性净资产</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>资产总额</t>
+  </si>
+  <si>
+    <t>负债总额</t>
+  </si>
+  <si>
+    <t>本届增加</t>
+  </si>
+  <si>
+    <t>净资产总额</t>
+  </si>
+  <si>
+    <t>本届减少</t>
+  </si>
+  <si>
+    <t>本届变动余额</t>
   </si>
 </sst>
 </file>
@@ -287,7 +329,7 @@
     <numFmt numFmtId="177" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="178" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,6 +405,30 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -440,7 +506,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -599,22 +665,55 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="12" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1157,11 +1256,11 @@
       <c r="C31" s="44"/>
     </row>
     <row r="32" spans="1:3" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="52" t="s">
+      <c r="A32" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B32" s="53"/>
-      <c r="C32" s="53"/>
+      <c r="B32" s="55"/>
+      <c r="C32" s="55"/>
     </row>
     <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.2">
       <c r="A33" s="51" t="s">
@@ -1417,11 +1516,11 @@
       <c r="C65" s="50"/>
     </row>
     <row r="66" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="52" t="s">
+      <c r="A66" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="B66" s="53"/>
-      <c r="C66" s="53"/>
+      <c r="B66" s="55"/>
+      <c r="C66" s="55"/>
     </row>
     <row r="67" spans="1:3" ht="15.75" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
@@ -1429,9 +1528,9 @@
       <c r="C67" s="8"/>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A68" s="54"/>
-      <c r="B68" s="55"/>
-      <c r="C68" s="55"/>
+      <c r="A68" s="52"/>
+      <c r="B68" s="53"/>
+      <c r="C68" s="53"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1669,4 +1768,514 @@
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A580C12-7F22-49B2-95D5-1169E9EFD06F}">
+  <dimension ref="A1:O33"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="17.375" style="63" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.25" style="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.375" style="63" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.375" style="63" customWidth="1"/>
+    <col min="5" max="5" width="14.5" style="63" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="63" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="17.375" style="63" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.875" style="63" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="60"/>
+    <col min="11" max="11" width="8.625" style="60" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.25" style="60" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16.5" style="60" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.75" style="60" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.875" style="60"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" s="59"/>
+      <c r="F1" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="G1" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" s="58" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A2" s="61" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="61" t="s">
+        <v>81</v>
+      </c>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A3" s="61" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="61" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A4" s="61" t="s">
+        <v>90</v>
+      </c>
+      <c r="B4" s="61"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="61" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="K4" s="62"/>
+      <c r="L4" s="62"/>
+      <c r="M4" s="62"/>
+      <c r="N4" s="62"/>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A5" s="59"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="61" t="s">
+        <v>82</v>
+      </c>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="F9" s="62"/>
+      <c r="G9" s="62"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="62"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A10" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="E10" s="59"/>
+      <c r="F10" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="H10" s="58" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="58" t="s">
+        <v>92</v>
+      </c>
+      <c r="K10" s="62"/>
+      <c r="L10" s="62"/>
+      <c r="M10" s="62"/>
+      <c r="N10" s="62"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A11" s="61"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A12" s="61"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="L12" s="62"/>
+      <c r="M12" s="62"/>
+      <c r="N12" s="62"/>
+      <c r="O12" s="62"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A13" s="64"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="64"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A14" s="64"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="61"/>
+      <c r="H14" s="61"/>
+      <c r="I14" s="61"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A15" s="64"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="64"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
+      <c r="I15" s="61"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A16" s="64"/>
+      <c r="B16" s="61"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="64"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="64"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="64"/>
+      <c r="B18" s="61"/>
+      <c r="C18" s="61"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="64"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="64"/>
+      <c r="B19" s="61"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="64"/>
+      <c r="B20" s="61"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="64"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="64"/>
+      <c r="B21" s="61"/>
+      <c r="C21" s="61"/>
+      <c r="D21" s="61"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="61"/>
+      <c r="H21" s="61"/>
+      <c r="I21" s="61"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="64"/>
+      <c r="B22" s="61"/>
+      <c r="C22" s="61"/>
+      <c r="D22" s="61"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="64"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="64"/>
+      <c r="B23" s="61"/>
+      <c r="C23" s="61"/>
+      <c r="D23" s="61"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="64"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="64"/>
+      <c r="B24" s="61"/>
+      <c r="C24" s="61"/>
+      <c r="D24" s="61"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="64"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="64"/>
+      <c r="B25" s="61"/>
+      <c r="C25" s="61"/>
+      <c r="D25" s="61"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="64"/>
+      <c r="G25" s="61"/>
+      <c r="H25" s="61"/>
+      <c r="I25" s="61"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="64"/>
+      <c r="B26" s="61"/>
+      <c r="C26" s="61"/>
+      <c r="D26" s="61"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="64"/>
+      <c r="G26" s="61"/>
+      <c r="H26" s="61"/>
+      <c r="I26" s="61"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="64"/>
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="64"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="64"/>
+      <c r="B28" s="61"/>
+      <c r="C28" s="61"/>
+      <c r="D28" s="61"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="61"/>
+      <c r="H28" s="61"/>
+      <c r="I28" s="61"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="64"/>
+      <c r="B29" s="61"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="64"/>
+      <c r="B30" s="61"/>
+      <c r="C30" s="61"/>
+      <c r="D30" s="61"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="64"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="64"/>
+      <c r="B31" s="61"/>
+      <c r="C31" s="61"/>
+      <c r="D31" s="61"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="64"/>
+      <c r="B32" s="61"/>
+      <c r="C32" s="61"/>
+      <c r="D32" s="61"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="64"/>
+      <c r="G32" s="61"/>
+      <c r="H32" s="61"/>
+      <c r="I32" s="61"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="64"/>
+      <c r="B33" s="61"/>
+      <c r="C33" s="61"/>
+      <c r="D33" s="61"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="61"/>
+      <c r="H33" s="61"/>
+      <c r="I33" s="61"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="K4:N4"/>
+    <mergeCell ref="F9:I9"/>
+    <mergeCell ref="K10:N10"/>
+    <mergeCell ref="L12:O12"/>
+  </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8AE1899-FA62-4ECC-89B9-A816C2BE9CED}">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="68"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="65"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+    </row>
+    <row r="2" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="17" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="18" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="19" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="20" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="22" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A35E14EC-3191-412C-859A-56A54FD373F1}">
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="16384" width="9" style="68"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="66" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="65"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+    </row>
+    <row r="2" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="3" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="4" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="6" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="8" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="10" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="11" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="12" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="13" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="14" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="15" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="16" spans="1:10" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="17" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="18" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="19" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="20" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="22" s="67" customFormat="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>